--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104673_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104673_W24.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8516</v>
+        <v>3.0931</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8802</v>
+        <v>2.308</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9714</v>
+        <v>0.7852</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2906</v>
+        <v>1.2964</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0982</v>
+        <v>2.0913</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8076</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.404</v>
+        <v>1.377</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1157</v>
+        <v>2.0922</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1134</v>
+        <v>-0.0806</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0176</v>
+        <v>-0.0009</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0958</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8954</v>
+        <v>0.1429</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6252</v>
+        <v>1.0982</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7298</v>
+        <v>-0.9552</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8651</v>
+        <v>1.3618</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1886</v>
+        <v>-1.2156</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0536</v>
+        <v>2.5775</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7499</v>
+        <v>0.7488</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5598</v>
+        <v>2.5618</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8099</v>
+        <v>-1.813</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3089</v>
+        <v>-0.3323</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6797</v>
+        <v>1.672</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.9886</v>
+        <v>-2.0042</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0587</v>
+        <v>1.081</v>
       </c>
       <c r="N3" t="n">
-        <v>0.88</v>
+        <v>0.8898</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7277</v>
+        <v>0.2276</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3206</v>
+        <v>0.3246</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4071</v>
+        <v>-0.097</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. NZOSA</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.063</v>
+        <v>0.7164</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7306</v>
+        <v>-0.1637</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7936</v>
+        <v>0.8801</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8839</v>
+        <v>-2.4335</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0202</v>
+        <v>-0.2083</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8637</v>
+        <v>-2.2252</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.7604</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7344000000000001</v>
+        <v>0.2231</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0373</v>
+        <v>-0.9835</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5809</v>
+        <v>-1.6731</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7546</v>
+        <v>-0.4314</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8264</v>
+        <v>-1.2417</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2268</v>
+        <v>2.0487</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3652</v>
+        <v>-0.3752</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5383</v>
+        <v>-0.2652</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8269</v>
+        <v>-0.11</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7712</v>
+        <v>1.4764</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3214</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>Y. NZOSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.383</v>
+        <v>0.5514</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8248</v>
+        <v>-1.3884</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4418</v>
+        <v>1.9398</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.4138</v>
+        <v>0.8946</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1828</v>
+        <v>0.0228</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.231</v>
+        <v>0.8718</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7168</v>
+        <v>-0.7007</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2589</v>
+        <v>-0.7379</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.9756</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6971</v>
+        <v>1.5953</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4417</v>
+        <v>0.7608</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2554</v>
+        <v>0.8345</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0415</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4889</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9739</v>
+        <v>-0.1838</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5151</v>
+        <v>-0.7058</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4783</v>
+        <v>0.7739</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3856</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4811</v>
+        <v>0.0002</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0473</v>
+        <v>-0.6959</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5662</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0413</v>
+        <v>-0.0393</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4891</v>
+        <v>0.491</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5304</v>
+        <v>-0.5303</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6666</v>
+        <v>-0.1881</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2782</v>
+        <v>0.0765</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3883</v>
+        <v>-0.2647</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4966</v>
+        <v>-0.3039</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3764</v>
+        <v>-2.3239</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8798</v>
+        <v>2.02</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0414</v>
+        <v>2.0345</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5123</v>
+        <v>4.5012</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4709</v>
+        <v>-2.4666</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4834</v>
+        <v>0.4345</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7435</v>
+        <v>3.7124</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.2601</v>
+        <v>-3.2779</v>
       </c>
       <c r="M7" t="n">
-        <v>1.558</v>
+        <v>1.6001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7688</v>
+        <v>0.7887</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7892</v>
+        <v>0.8113</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R7" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0201</v>
+        <v>-0.8117</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2874</v>
+        <v>0.4104</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3075</v>
+        <v>-1.2221</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3307</v>
+        <v>-1.1664</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5382</v>
+        <v>-0.3254</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7925</v>
+        <v>-0.841</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0646</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0014</v>
+        <v>-0.0028</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0798</v>
+        <v>-0.0618</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3969</v>
+        <v>-0.4156</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4715</v>
+        <v>-0.4901</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3157</v>
+        <v>0.3511</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4701</v>
+        <v>0.4873</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1545</v>
+        <v>-0.1362</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6766</v>
+        <v>-0.5375</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0998</v>
+        <v>0.1389</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5768</v>
+        <v>-0.6764</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9703</v>
+        <v>-2.3014</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7162</v>
+        <v>-2.3213</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2541</v>
+        <v>0.0198</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3391</v>
+        <v>-2.3384</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4732</v>
+        <v>-0.4766</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8658</v>
+        <v>-1.8618</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2969</v>
+        <v>-2.314</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7242</v>
+        <v>-0.7347</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0422</v>
+        <v>-0.0245</v>
       </c>
       <c r="N9" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3273</v>
+        <v>-0.0117</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8075</v>
+        <v>0.2203</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4803</v>
+        <v>-0.232</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1851</v>
+        <v>-3.5114</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8191</v>
+        <v>-6.1611</v>
       </c>
       <c r="F10" t="n">
-        <v>0.634</v>
+        <v>2.6497</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.397</v>
+        <v>-0.6108</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7372</v>
+        <v>-1.7176</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.6597</v>
+        <v>1.1068</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.671</v>
+        <v>-3.6567</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9706</v>
+        <v>-3.0379</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.7003</v>
+        <v>-0.6188</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.726</v>
+        <v>3.0459</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2334</v>
+        <v>1.3203</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9594</v>
+        <v>1.7256</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-3.8697</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5314</v>
+        <v>-1.3982</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2128</v>
+        <v>0.2759</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6814</v>
+        <v>-1.6741</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="11">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.006</v>
+        <v>-3.621</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5988</v>
+        <v>-2.2523</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4072</v>
+        <v>-1.3687</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.9287</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3449</v>
+        <v>-0.3419</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9513</v>
+        <v>-0.946</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4842</v>
+        <v>-0.0988</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1706</v>
+        <v>-4.0739</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.4745</v>
+        <v>-4.2202</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3039</v>
+        <v>0.1463</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6138</v>
+        <v>-4.4004</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.72</v>
+        <v>-0.7435</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1062</v>
+        <v>-3.6569</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.6294</v>
+        <v>-3.7201</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.0242</v>
+        <v>-1.0007</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6052</v>
+        <v>-2.7194</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0156</v>
+        <v>-0.6803</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3042</v>
+        <v>0.2572</v>
       </c>
       <c r="O12" t="n">
-        <v>1.7114</v>
+        <v>-0.9375</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2683</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.8562</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0596</v>
+        <v>-0.3564</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.8657</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.978</v>
+        <v>-1.2221</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.2437</v>
+        <v>-9.255100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.4343</v>
+        <v>-18.7598</v>
       </c>
       <c r="F13" t="n">
-        <v>9.190500000000002</v>
+        <v>9.504799999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.854400000000002</v>
+        <v>-5.8414</v>
       </c>
       <c r="H13" t="n">
-        <v>6.220099999999999</v>
+        <v>6.1774</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.0743</v>
+        <v>-12.0187</v>
       </c>
       <c r="J13" t="n">
-        <v>-10.5813</v>
+        <v>-10.8435</v>
       </c>
       <c r="K13" t="n">
-        <v>1.907499999999999</v>
+        <v>1.732799999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-12.4887</v>
+        <v>-12.5762</v>
       </c>
       <c r="M13" t="n">
-        <v>4.7266</v>
+        <v>5.002</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3124</v>
+        <v>4.4445</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4143000000000001</v>
+        <v>0.5574000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.1466</v>
+        <v>-18.2104</v>
       </c>
       <c r="R13" t="n">
-        <v>17.0124</v>
+        <v>17.0724</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.2794</v>
+        <v>-4.2967</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9339</v>
+        <v>2.9683</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.2134</v>
+        <v>-7.265099999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>2.0246</v>
+        <v>2.0211</v>
       </c>
       <c r="W13" t="n">
-        <v>7.359799999999999</v>
+        <v>7.3258</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.335</v>
+        <v>-5.304399999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3655</v>
+        <v>3.9916</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2328</v>
+        <v>1.7467</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1327</v>
+        <v>2.245</v>
       </c>
       <c r="G14" t="n">
-        <v>0.374</v>
+        <v>0.677</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4572</v>
+        <v>1.3845</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8312</v>
+        <v>-0.7075</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.7565</v>
+        <v>-0.4012</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.975</v>
+        <v>1.1409</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2185</v>
+        <v>-1.542</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1306</v>
+        <v>1.0782</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5178</v>
+        <v>0.2437</v>
       </c>
       <c r="O14" t="n">
-        <v>1.6127</v>
+        <v>0.8345</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8158</v>
+        <v>0.6317</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9893</v>
+        <v>0.7428</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1735</v>
+        <v>-0.1111</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4849</v>
+        <v>3.7435</v>
       </c>
       <c r="E15" t="n">
-        <v>1.298</v>
+        <v>1.1658</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1869</v>
+        <v>2.5778</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6792</v>
+        <v>1.0026</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3882</v>
+        <v>0.8497</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.709</v>
+        <v>0.1529</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3823</v>
+        <v>-0.3902</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1531</v>
+        <v>0.348</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.5354</v>
+        <v>-0.7382</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0614</v>
+        <v>1.3928</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2351</v>
+        <v>0.5018</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8264</v>
+        <v>0.8911</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1252</v>
+        <v>0.2856</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2662</v>
+        <v>0.4665</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.141</v>
+        <v>-0.1808</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4141</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9841</v>
+        <v>2.9442</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8383</v>
+        <v>-0.7058</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1459</v>
+        <v>3.65</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0077</v>
+        <v>2.3656</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8426</v>
+        <v>1.4642</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1652</v>
+        <v>0.9014</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3633</v>
+        <v>0.1979</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3565</v>
+        <v>0.0862</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7198</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>1.371</v>
+        <v>2.1677</v>
       </c>
       <c r="N16" t="n">
-        <v>0.486</v>
+        <v>1.378</v>
       </c>
       <c r="O16" t="n">
-        <v>0.885</v>
+        <v>0.7896</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4773</v>
+        <v>0.5786</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1089</v>
+        <v>0.2345</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5861</v>
+        <v>0.3441</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6487</v>
+        <v>2.8359</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0566</v>
+        <v>0.2022</v>
       </c>
       <c r="F17" t="n">
-        <v>3.7053</v>
+        <v>2.6337</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3526</v>
+        <v>0.3625</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4543</v>
+        <v>-1.4698</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8983</v>
+        <v>1.8323</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1985</v>
+        <v>-1.7924</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0866</v>
+        <v>-2.0004</v>
       </c>
       <c r="L17" t="n">
-        <v>0.112</v>
+        <v>0.2081</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1541</v>
+        <v>2.1548</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3678</v>
+        <v>0.5306</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7864</v>
+        <v>1.6242</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.2763</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2961</v>
+        <v>1.2866</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.121</v>
+        <v>1.9946</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4171</v>
+        <v>-0.708</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9411</v>
+        <v>1.8897</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8669</v>
+        <v>0.9034</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0741</v>
+        <v>0.9863</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8702</v>
+        <v>5.3692</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.5729</v>
+        <v>-0.6927</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7027</v>
+        <v>6.0619</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7814</v>
+        <v>4.8235</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.1859</v>
+        <v>0.3857</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4045</v>
+        <v>4.4377</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0888</v>
+        <v>0.5457</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.387</v>
+        <v>-1.0784</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2982</v>
+        <v>1.6242</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8147</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-5.6908</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3181</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6483</v>
+        <v>0.1365</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3303</v>
+        <v>-0.2016</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3214</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2988</v>
+        <v>1.7387</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9117</v>
+        <v>0.2456</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2105</v>
+        <v>1.493</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8653</v>
+        <v>-0.877</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.886</v>
+        <v>-3.562</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7513</v>
+        <v>2.685</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3435</v>
+        <v>-0.8199</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6793</v>
+        <v>-2.1966</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3359</v>
+        <v>1.3767</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2088</v>
+        <v>-0.0571</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2066</v>
+        <v>-1.3654</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4154</v>
+        <v>1.3083</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>1.8211</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1809</v>
+        <v>1.1101</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4053</v>
+        <v>1.0655</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5861</v>
+        <v>0.0446</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1607</v>
+        <v>-0.3155</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0854</v>
+        <v>1.673</v>
       </c>
       <c r="E20" t="n">
-        <v>0.616</v>
+        <v>-0.8153</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4694</v>
+        <v>2.4883</v>
       </c>
       <c r="G20" t="n">
-        <v>5.377</v>
+        <v>0.8718</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7029</v>
+        <v>-0.8847</v>
       </c>
       <c r="I20" t="n">
-        <v>6.0799</v>
+        <v>1.7565</v>
       </c>
       <c r="J20" t="n">
-        <v>4.8686</v>
+        <v>-0.3618</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4014</v>
+        <v>-0.697</v>
       </c>
       <c r="L20" t="n">
-        <v>4.4672</v>
+        <v>0.3351</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5085</v>
+        <v>1.2336</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1043</v>
+        <v>-0.1877</v>
       </c>
       <c r="O20" t="n">
-        <v>1.6127</v>
+        <v>1.4214</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.4025</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.6708</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8892</v>
+        <v>0.1881</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2208</v>
+        <v>0.5269</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6684</v>
+        <v>-0.3388</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>1.639</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7733</v>
+        <v>0.1787</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9896</v>
+        <v>-2.8999</v>
       </c>
       <c r="F21" t="n">
-        <v>3.763</v>
+        <v>3.0786</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0541</v>
+        <v>2.0621</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1585</v>
+        <v>1.1684</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8956</v>
+        <v>0.8937</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2163</v>
+        <v>0.1967</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8934</v>
+        <v>0.8823</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6771</v>
+        <v>-0.6856</v>
       </c>
       <c r="M21" t="n">
-        <v>1.8379</v>
+        <v>1.8653</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2652</v>
+        <v>0.2861</v>
       </c>
       <c r="O21" t="n">
-        <v>1.5727</v>
+        <v>1.5793</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2409</v>
+        <v>0.6401</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1966</v>
+        <v>0.3178</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0443</v>
+        <v>0.3223</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7443</v>
+        <v>-1.7877</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8482</v>
+        <v>-1.0953</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8961</v>
+        <v>-0.6924</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3016</v>
+        <v>-1.3033</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.179</v>
+        <v>-1.1749</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1227</v>
+        <v>-0.1284</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1476</v>
+        <v>-1.1601</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.154</v>
+        <v>-0.1432</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1963</v>
+        <v>0.1498</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2994</v>
+        <v>0.0648</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1031</v>
+        <v>0.0849</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9715</v>
+        <v>-2.0146</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3966</v>
+        <v>-2.6029</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4251</v>
+        <v>0.5883</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8333</v>
+        <v>-1.8384</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1775</v>
+        <v>-1.1721</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6558</v>
+        <v>-0.6663</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1067</v>
+        <v>-2.1405</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1527</v>
+        <v>-0.1659</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.954</v>
+        <v>-1.9747</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2734</v>
+        <v>0.3021</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0248</v>
+        <v>-1.0062</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2982</v>
+        <v>1.3083</v>
       </c>
       <c r="P23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7694</v>
+        <v>0.1833</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1331</v>
+        <v>0.6985</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6364</v>
+        <v>-0.5152</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4102</v>
+        <v>-2.4082</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.1568</v>
+        <v>-1.1609</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="24">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6223</v>
+        <v>-4.3062</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.7718</v>
+        <v>-6.5808</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1496</v>
+        <v>2.2746</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8503</v>
+        <v>-2.8507</v>
       </c>
       <c r="H24" t="n">
         <v>-2.088</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7623</v>
+        <v>-0.7627</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.1287</v>
+        <v>-3.154</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4413</v>
+        <v>-1.4554</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.6874</v>
+        <v>-1.6987</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2784</v>
+        <v>0.3033</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S24" t="n">
-        <v>0.604</v>
+        <v>0.9394</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7743</v>
+        <v>1.0168</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1703</v>
+        <v>-0.0774</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.243700000000004</v>
+        <v>10.8868</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.1225</v>
+        <v>-10.4363</v>
       </c>
       <c r="F25" t="n">
-        <v>19.3664</v>
+        <v>21.3232</v>
       </c>
       <c r="G25" t="n">
-        <v>5.854499999999999</v>
+        <v>5.8414</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.2199</v>
+        <v>-6.1774</v>
       </c>
       <c r="I25" t="n">
-        <v>12.0744</v>
+        <v>12.0188</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.726599999999999</v>
+        <v>-5.001999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.312200000000001</v>
+        <v>-4.444599999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4142000000000001</v>
+        <v>-0.5575999999999994</v>
       </c>
       <c r="M25" t="n">
-        <v>10.5813</v>
+        <v>10.8432</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.9074</v>
+        <v>-1.732600000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>12.4886</v>
+        <v>12.5762</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q25" t="n">
-        <v>-17.0125</v>
+        <v>-17.0725</v>
       </c>
       <c r="R25" t="n">
-        <v>18.1466</v>
+        <v>18.2106</v>
       </c>
       <c r="S25" t="n">
-        <v>4.279599999999999</v>
+        <v>5.928199999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>7.213400000000001</v>
+        <v>7.265199999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.9338</v>
+        <v>-1.337</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.0246</v>
+        <v>-2.021199999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>4.4031</v>
+        <v>4.372800000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.4277</v>
+        <v>-6.3939</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104673_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104673_W24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.304399999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104673_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.3939</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
